--- a/Projects/Cade Cunningham.xlsx
+++ b/Projects/Cade Cunningham.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thejjserg/Documents/GitHub/basketball-analytics/Projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C2E564-1A0A-3542-8502-067C6EDF89BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BFF7220-6D1D-214D-90C8-92C8EF071C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17580" xr2:uid="{91DDF0CC-1112-E742-B0ED-4CCF8B231B63}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17580" activeTab="3" xr2:uid="{91DDF0CC-1112-E742-B0ED-4CCF8B231B63}"/>
   </bookViews>
   <sheets>
     <sheet name="Per Game" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
     <sheet name="College Stats" sheetId="12" r:id="rId11"/>
     <sheet name="Resources" sheetId="9" r:id="rId12"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="165">
   <si>
     <t>Season</t>
   </si>
@@ -575,11 +575,20 @@
   <si>
     <t>https://www.basketball-reference.com/players/c/cunnica01.html</t>
   </si>
+  <si>
+    <t>BadPass_PCT</t>
+  </si>
+  <si>
+    <t>LostBall_PCT</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="171" formatCode="0.000"/>
+  </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -655,7 +664,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
@@ -666,6 +675,9 @@
     <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="46" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -6374,7 +6386,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F589270-2DF2-4841-81B4-F528C00C7DAE}">
-  <dimension ref="A1:Y12"/>
+  <dimension ref="A1:AA17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
@@ -6394,17 +6406,19 @@
     <col min="15" max="15" width="23.1640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="17.5" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="4.83203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6457,31 +6471,37 @@
         <v>83</v>
       </c>
       <c r="R1" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>146</v>
       </c>
@@ -6533,32 +6553,38 @@
       <c r="Q2" s="3">
         <v>67</v>
       </c>
-      <c r="R2" s="3">
+      <c r="R2" s="10">
+        <v>0.64736842105263159</v>
+      </c>
+      <c r="S2" s="10">
+        <v>0.35263157894736841</v>
+      </c>
+      <c r="T2" s="3">
         <v>93</v>
       </c>
-      <c r="S2" s="3">
+      <c r="U2" s="3">
         <v>25</v>
       </c>
-      <c r="T2" s="3">
+      <c r="V2" s="3">
         <v>61</v>
       </c>
-      <c r="U2" s="3">
+      <c r="W2" s="3">
         <v>5</v>
       </c>
-      <c r="V2" s="3">
+      <c r="X2" s="3">
         <v>837</v>
       </c>
-      <c r="W2" s="3">
+      <c r="Y2" s="3">
         <v>14</v>
       </c>
-      <c r="X2" s="3">
+      <c r="Z2" s="3">
         <v>77</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="AA2" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>151</v>
       </c>
@@ -6610,30 +6636,36 @@
       <c r="Q3" s="3">
         <v>11</v>
       </c>
-      <c r="R3" s="3">
+      <c r="R3" s="11">
+        <v>0.65625</v>
+      </c>
+      <c r="S3" s="11">
+        <v>0.34375</v>
+      </c>
+      <c r="T3" s="3">
         <v>16</v>
       </c>
-      <c r="S3" s="3">
+      <c r="U3" s="3">
         <v>5</v>
       </c>
-      <c r="T3" s="3">
+      <c r="V3" s="3">
         <v>18</v>
       </c>
-      <c r="U3" s="3">
+      <c r="W3" s="3">
         <v>2</v>
       </c>
-      <c r="V3" s="3">
+      <c r="X3" s="3">
         <v>176</v>
       </c>
-      <c r="W3" s="3">
+      <c r="Y3" s="3">
         <v>3</v>
       </c>
-      <c r="X3" s="3">
+      <c r="Z3" s="3">
         <v>23</v>
       </c>
-      <c r="Y3" s="3"/>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="AA3" s="3"/>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>153</v>
       </c>
@@ -6685,30 +6717,36 @@
       <c r="Q4" s="3">
         <v>59</v>
       </c>
-      <c r="R4" s="3">
+      <c r="R4" s="12">
+        <v>0.68108108108108112</v>
+      </c>
+      <c r="S4" s="11">
+        <v>0.31891891891891888</v>
+      </c>
+      <c r="T4" s="3">
         <v>81</v>
       </c>
-      <c r="S4" s="3">
+      <c r="U4" s="3">
         <v>13</v>
       </c>
-      <c r="T4" s="3">
+      <c r="V4" s="3">
         <v>109</v>
       </c>
-      <c r="U4" s="3">
+      <c r="W4" s="3">
         <v>6</v>
       </c>
-      <c r="V4" s="3">
+      <c r="X4" s="3">
         <v>1076</v>
       </c>
-      <c r="W4" s="3">
+      <c r="Y4" s="3">
         <v>21</v>
       </c>
-      <c r="X4" s="3">
+      <c r="Z4" s="3">
         <v>92</v>
       </c>
-      <c r="Y4" s="3"/>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="AA4" s="3"/>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>154</v>
       </c>
@@ -6760,32 +6798,38 @@
       <c r="Q5" s="3">
         <v>105</v>
       </c>
-      <c r="R5" s="3">
+      <c r="R5" s="12">
+        <v>0.62230215827338131</v>
+      </c>
+      <c r="S5" s="11">
+        <v>0.37769784172661869</v>
+      </c>
+      <c r="T5" s="3">
         <v>87</v>
       </c>
-      <c r="S5" s="3">
+      <c r="U5" s="3">
         <v>15</v>
       </c>
-      <c r="T5" s="3">
+      <c r="V5" s="3">
         <v>165</v>
       </c>
-      <c r="U5" s="3">
+      <c r="W5" s="3">
         <v>6</v>
       </c>
-      <c r="V5" s="3">
+      <c r="X5" s="3">
         <v>1511</v>
       </c>
-      <c r="W5" s="3">
+      <c r="Y5" s="3">
         <v>39</v>
       </c>
-      <c r="X5" s="3">
+      <c r="Z5" s="3">
         <v>100</v>
       </c>
-      <c r="Y5" s="8" t="s">
+      <c r="AA5" s="8" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>156</v>
       </c>
@@ -6837,30 +6881,36 @@
       <c r="Q6" s="3">
         <v>38</v>
       </c>
-      <c r="R6" s="3">
+      <c r="R6" s="12">
+        <v>0.69841269841269837</v>
+      </c>
+      <c r="S6" s="11">
+        <v>0.30158730158730163</v>
+      </c>
+      <c r="T6" s="3">
         <v>57</v>
-      </c>
-      <c r="S6" s="3">
-        <v>7</v>
-      </c>
-      <c r="T6" s="3">
-        <v>109</v>
       </c>
       <c r="U6" s="3">
         <v>7</v>
       </c>
       <c r="V6" s="3">
+        <v>109</v>
+      </c>
+      <c r="W6" s="3">
+        <v>7</v>
+      </c>
+      <c r="X6" s="3">
         <v>798</v>
       </c>
-      <c r="W6" s="3">
+      <c r="Y6" s="3">
         <v>27</v>
       </c>
-      <c r="X6" s="3">
+      <c r="Z6" s="3">
         <v>37</v>
       </c>
-      <c r="Y6" s="3"/>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="AA6" s="3"/>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
       <c r="B7" s="3"/>
       <c r="C7" s="2"/>
@@ -6886,8 +6936,10 @@
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
       <c r="Y7" s="3"/>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="3"/>
+      <c r="AA7" s="3"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="3"/>
       <c r="C8" s="2"/>
@@ -6913,8 +6965,10 @@
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3"/>
+      <c r="AA8" s="3"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -6940,8 +6994,10 @@
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3"/>
+      <c r="AA9" s="3"/>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
       <c r="B10" s="4"/>
       <c r="C10" s="2"/>
@@ -6967,8 +7023,10 @@
       <c r="W10" s="4"/>
       <c r="X10" s="4"/>
       <c r="Y10" s="4"/>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="4"/>
+      <c r="AA10" s="4"/>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
       <c r="B11" s="4"/>
       <c r="C11" s="2"/>
@@ -6988,14 +7046,14 @@
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
       <c r="S11" s="4"/>
-      <c r="T11" s="4"/>
-      <c r="U11" s="4"/>
       <c r="V11" s="4"/>
       <c r="W11" s="4"/>
       <c r="X11" s="4"/>
       <c r="Y11" s="4"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="4"/>
+      <c r="AA11" s="4"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
       <c r="B12" s="3"/>
       <c r="C12" s="2"/>
@@ -7015,19 +7073,36 @@
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
-      <c r="U12" s="3"/>
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
+      <c r="Z12" s="3"/>
+      <c r="AA12" s="3"/>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="V13" s="3"/>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="V14" s="3"/>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="V15" s="3"/>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="21:22" x14ac:dyDescent="0.2">
+      <c r="U17" s="3"/>
+      <c r="V17" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" display="https://www.basketball-reference.com/players/c/cunnica01/gamelog/2022/" xr:uid="{C597A08D-6952-DF49-A355-DF6EEE5A5633}"/>
     <hyperlink ref="C2" r:id="rId2" display="https://www.basketball-reference.com/teams/DET/2022.html" xr:uid="{A294FB55-4576-B04A-9CFF-68A3ACF8F22B}"/>
     <hyperlink ref="D2" r:id="rId3" display="https://www.basketball-reference.com/leagues/NBA_2022.html" xr:uid="{94DB266B-8404-DC42-A633-0C2F059BB3C7}"/>
-    <hyperlink ref="Y2" r:id="rId4" location="all_roy" display="https://www.basketball-reference.com/awards/awards_2022.html - all_roy" xr:uid="{35936673-1AE5-D14F-BAA8-A8E0B52D9165}"/>
+    <hyperlink ref="AA2" r:id="rId4" location="all_roy" display="https://www.basketball-reference.com/awards/awards_2022.html - all_roy" xr:uid="{35936673-1AE5-D14F-BAA8-A8E0B52D9165}"/>
     <hyperlink ref="A3" r:id="rId5" display="https://www.basketball-reference.com/players/c/cunnica01/gamelog/2023/" xr:uid="{F024EF36-22F7-2748-A33F-4287AF1AD395}"/>
     <hyperlink ref="C3" r:id="rId6" display="https://www.basketball-reference.com/teams/DET/2023.html" xr:uid="{BB66E928-E909-4340-93FD-28B411439F5A}"/>
     <hyperlink ref="D3" r:id="rId7" display="https://www.basketball-reference.com/leagues/NBA_2023.html" xr:uid="{44D51249-3BBD-4C4E-A746-1A894DB94D82}"/>
